--- a/Lakshmi1.xlsx
+++ b/Lakshmi1.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.6"/>
   <cols>
     <col width="21.109375" customWidth="1" style="1" min="1" max="2"/>
@@ -1206,82 +1206,2286 @@
         <v>113680</v>
       </c>
     </row>
-    <row r="26" ht="19.95" customHeight="1"/>
-    <row r="27" ht="19.95" customHeight="1"/>
-    <row r="28" ht="19.95" customHeight="1"/>
-    <row r="29" ht="19.95" customHeight="1"/>
-    <row r="30" ht="19.95" customHeight="1"/>
-    <row r="31" ht="19.95" customHeight="1"/>
-    <row r="32" ht="19.95" customHeight="1"/>
-    <row r="33" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="34" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="35" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="36" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="37" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="38" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="39" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="40" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="41" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="42" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="43" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="44" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="45" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="46" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="47" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="48" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="49" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="50" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="51" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="52" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="53" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="54" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="55" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="56" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="57" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="58" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="59" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="60" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="61" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="62" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="63" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="64" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="65" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="66" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="67" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="68" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="69" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="70" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="71" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="72" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="73" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="74" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="75" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="76" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="77" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="78" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="79" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="80" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="81" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="82" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="83" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="84" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="85" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="86" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="87" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="88" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="89" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="90" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="91" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="92" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="93" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="94" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="95" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="96" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="97" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="98" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="99" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="100" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="101" ht="19.95" customFormat="1" customHeight="1" s="1"/>
+    <row r="26" ht="19.95" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:52:23</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>127.05</v>
+      </c>
+      <c r="D26" t="n">
+        <v>129.85</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4004</v>
+      </c>
+      <c r="G26" t="n">
+        <v>505078</v>
+      </c>
+      <c r="H26" t="n">
+        <v>48770</v>
+      </c>
+    </row>
+    <row r="27" ht="19.95" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:56:36</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>116.85</v>
+      </c>
+      <c r="D27" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-8651.5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1290773</v>
+      </c>
+      <c r="H27" t="n">
+        <v>170165</v>
+      </c>
+    </row>
+    <row r="28" ht="19.95" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-01-30 12:00:36</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>116.15</v>
+      </c>
+      <c r="D28" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1072.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>548035</v>
+      </c>
+      <c r="H28" t="n">
+        <v>29517</v>
+      </c>
+    </row>
+    <row r="29" ht="19.95" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-01-30 12:06:29</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>117.95</v>
+      </c>
+      <c r="D29" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-8580</v>
+      </c>
+      <c r="G29" t="n">
+        <v>557491</v>
+      </c>
+      <c r="H29" t="n">
+        <v>30678</v>
+      </c>
+    </row>
+    <row r="30" ht="19.95" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-01-30 12:10:21</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>127</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F30" t="n">
+        <v>715</v>
+      </c>
+      <c r="G30" t="n">
+        <v>538650</v>
+      </c>
+      <c r="H30" t="n">
+        <v>49632</v>
+      </c>
+    </row>
+    <row r="31" ht="19.95" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-01-30 12:14:05</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>128.1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>130.95</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4075.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>543322</v>
+      </c>
+      <c r="H31" t="n">
+        <v>50149</v>
+      </c>
+    </row>
+    <row r="32" ht="19.95" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-01-30 12:17:32</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>117.55</v>
+      </c>
+      <c r="D32" t="n">
+        <v>118.9</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1930.5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1402620</v>
+      </c>
+      <c r="H32" t="n">
+        <v>170147</v>
+      </c>
+    </row>
+    <row r="33" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-01-30 12:20:47</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="D33" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-8580</v>
+      </c>
+      <c r="G33" t="n">
+        <v>590744</v>
+      </c>
+      <c r="H33" t="n">
+        <v>30001</v>
+      </c>
+    </row>
+    <row r="34" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-01-30 12:23:23</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>117.6</v>
+      </c>
+      <c r="D34" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4147</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1440448</v>
+      </c>
+      <c r="H34" t="n">
+        <v>164627</v>
+      </c>
+    </row>
+    <row r="35" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-01-30 12:25:21</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>122.8</v>
+      </c>
+      <c r="D35" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3003</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1466589</v>
+      </c>
+      <c r="H35" t="n">
+        <v>164945</v>
+      </c>
+    </row>
+    <row r="36" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-01-30 12:29:29</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="D36" t="n">
+        <v>116.15</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1930.5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1135928</v>
+      </c>
+      <c r="H36" t="n">
+        <v>64422</v>
+      </c>
+    </row>
+    <row r="37" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-01-30 12:32:04</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>124.7</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F37" t="n">
+        <v>286</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1518711</v>
+      </c>
+      <c r="H37" t="n">
+        <v>160733</v>
+      </c>
+    </row>
+    <row r="38" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-01-30 12:34:49</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>117.55</v>
+      </c>
+      <c r="D38" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1501.5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1148183</v>
+      </c>
+      <c r="H38" t="n">
+        <v>65713</v>
+      </c>
+    </row>
+    <row r="39" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-01-30 12:37:21</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NIFTY2620325400CE</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>159.7</v>
+      </c>
+      <c r="D39" t="n">
+        <v>160.1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F39" t="n">
+        <v>572</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1462063</v>
+      </c>
+      <c r="H39" t="n">
+        <v>116778</v>
+      </c>
+    </row>
+    <row r="40" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-01-30 12:39:02</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="D40" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>627669</v>
+      </c>
+      <c r="H40" t="n">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="41" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-01-30 12:41:19</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>115.75</v>
+      </c>
+      <c r="D41" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2502.5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1176733</v>
+      </c>
+      <c r="H41" t="n">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="42" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-01-30 13:09:48</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="D42" t="n">
+        <v>118.45</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1501.5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>683360</v>
+      </c>
+      <c r="H42" t="n">
+        <v>29108</v>
+      </c>
+    </row>
+    <row r="43" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-01-30 13:14:33</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>134.65</v>
+      </c>
+      <c r="D43" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3074.5</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1297398</v>
+      </c>
+      <c r="H43" t="n">
+        <v>60661</v>
+      </c>
+    </row>
+    <row r="44" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-01-30 13:16:32</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>153.5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>157.05</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5076.5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1328015</v>
+      </c>
+      <c r="H44" t="n">
+        <v>62861</v>
+      </c>
+    </row>
+    <row r="45" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-01-30 13:20:47</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>NIFTY2620325000PE</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="D45" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F45" t="n">
+        <v>572</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2072330</v>
+      </c>
+      <c r="H45" t="n">
+        <v>123062</v>
+      </c>
+    </row>
+    <row r="46" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-01-30 13:26:39</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>121.75</v>
+      </c>
+      <c r="D46" t="n">
+        <v>123</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1787.5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>714312</v>
+      </c>
+      <c r="H46" t="n">
+        <v>47297</v>
+      </c>
+    </row>
+    <row r="47" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-01-30 13:29:58</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>NIFTY2620325000PE</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="D47" t="n">
+        <v>118.15</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1072.5</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2132741</v>
+      </c>
+      <c r="H47" t="n">
+        <v>125572</v>
+      </c>
+    </row>
+    <row r="48" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-01-30 13:33:07</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>125.75</v>
+      </c>
+      <c r="D48" t="n">
+        <v>126.35</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F48" t="n">
+        <v>858</v>
+      </c>
+      <c r="G48" t="n">
+        <v>726963</v>
+      </c>
+      <c r="H48" t="n">
+        <v>47623</v>
+      </c>
+    </row>
+    <row r="49" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-01-30 13:34:59</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>126.3</v>
+      </c>
+      <c r="D49" t="n">
+        <v>126.95</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F49" t="n">
+        <v>929.5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>732197</v>
+      </c>
+      <c r="H49" t="n">
+        <v>47623</v>
+      </c>
+    </row>
+    <row r="50" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-01-30 13:37:35</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>127.55</v>
+      </c>
+      <c r="D50" t="n">
+        <v>128</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F50" t="n">
+        <v>643.5</v>
+      </c>
+      <c r="G50" t="n">
+        <v>737612</v>
+      </c>
+      <c r="H50" t="n">
+        <v>47906</v>
+      </c>
+    </row>
+    <row r="51" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-01-30 13:40:48</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>NIFTY2620325550CE</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="D51" t="n">
+        <v>101</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1573</v>
+      </c>
+      <c r="G51" t="n">
+        <v>745612</v>
+      </c>
+      <c r="H51" t="n">
+        <v>48206</v>
+      </c>
+    </row>
+    <row r="52" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-01-30 13:43:52</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="D52" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1287</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1935262</v>
+      </c>
+      <c r="H52" t="n">
+        <v>189384</v>
+      </c>
+    </row>
+    <row r="53" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-01-30 13:46:36</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="D53" t="n">
+        <v>117.45</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1215.5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1518143</v>
+      </c>
+      <c r="H53" t="n">
+        <v>58529</v>
+      </c>
+    </row>
+    <row r="54" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-01-30 13:48:39</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>123.1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>123.45</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F54" t="n">
+        <v>500.5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1527386</v>
+      </c>
+      <c r="H54" t="n">
+        <v>60709</v>
+      </c>
+    </row>
+    <row r="55" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-01-30 13:51:15</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="D55" t="n">
+        <v>123.7</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F55" t="n">
+        <v>286</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2017207</v>
+      </c>
+      <c r="H55" t="n">
+        <v>164801</v>
+      </c>
+    </row>
+    <row r="56" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-01-30 13:53:03</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>124.8</v>
+      </c>
+      <c r="D56" t="n">
+        <v>125.55</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1072.5</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2037622</v>
+      </c>
+      <c r="H56" t="n">
+        <v>158848</v>
+      </c>
+    </row>
+    <row r="57" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-01-30 13:54:41</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="D57" t="n">
+        <v>132.25</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1072.5</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2056387</v>
+      </c>
+      <c r="H57" t="n">
+        <v>158807</v>
+      </c>
+    </row>
+    <row r="58" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-01-30 13:59:43</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>NIFTY2620325550CE</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>122.05</v>
+      </c>
+      <c r="D58" t="n">
+        <v>122.9</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1215.5</v>
+      </c>
+      <c r="G58" t="n">
+        <v>828086</v>
+      </c>
+      <c r="H58" t="n">
+        <v>43474</v>
+      </c>
+    </row>
+    <row r="59" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-01-30 14:01:39</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>NIFTY2620325650CE</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="D59" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1072.5</v>
+      </c>
+      <c r="G59" t="n">
+        <v>579106</v>
+      </c>
+      <c r="H59" t="n">
+        <v>44124</v>
+      </c>
+    </row>
+    <row r="60" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-01-30 14:04:42</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>NIFTY2620325150PE</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>123.15</v>
+      </c>
+      <c r="D60" t="n">
+        <v>124.15</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1430</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1233195</v>
+      </c>
+      <c r="H60" t="n">
+        <v>33992</v>
+      </c>
+    </row>
+    <row r="61" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-01-30 14:07:33</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>NIFTY2620325650CE</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>98.34999999999999</v>
+      </c>
+      <c r="D61" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F61" t="n">
+        <v>500.5</v>
+      </c>
+      <c r="G61" t="n">
+        <v>604036</v>
+      </c>
+      <c r="H61" t="n">
+        <v>44051</v>
+      </c>
+    </row>
+    <row r="62" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-01-30 14:10:52</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>NIFTY2620325600CE</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>120.95</v>
+      </c>
+      <c r="D62" t="n">
+        <v>114.75</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-8866</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1395008</v>
+      </c>
+      <c r="H62" t="n">
+        <v>85932</v>
+      </c>
+    </row>
+    <row r="63" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-01-30 14:15:01</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>NIFTY2620325550CE</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>129</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2717</v>
+      </c>
+      <c r="G63" t="n">
+        <v>931849</v>
+      </c>
+      <c r="H63" t="n">
+        <v>39194</v>
+      </c>
+    </row>
+    <row r="64" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-01-30 14:18:46</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>NIFTY2620325150PE</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>118.9</v>
+      </c>
+      <c r="D64" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-429</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1261354</v>
+      </c>
+      <c r="H64" t="n">
+        <v>35767</v>
+      </c>
+    </row>
+    <row r="65" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-01-30 14:21:15</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>NIFTY2620325550CE</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>129.85</v>
+      </c>
+      <c r="D65" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F65" t="n">
+        <v>929.5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>943848</v>
+      </c>
+      <c r="H65" t="n">
+        <v>39051</v>
+      </c>
+    </row>
+    <row r="66" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-01-30 14:27:40</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>NIFTY2620325150PE</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="D66" t="n">
+        <v>123.75</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2216.5</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1272597</v>
+      </c>
+      <c r="H66" t="n">
+        <v>36482</v>
+      </c>
+    </row>
+    <row r="67" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-01-30 14:31:35</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>NIFTY2620325550CE</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>120.3</v>
+      </c>
+      <c r="D67" t="n">
+        <v>114</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-9009</v>
+      </c>
+      <c r="G67" t="n">
+        <v>975621</v>
+      </c>
+      <c r="H67" t="n">
+        <v>37451</v>
+      </c>
+    </row>
+    <row r="68" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-01-30 14:38:14</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>NIFTY2620325150PE</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>128.35</v>
+      </c>
+      <c r="D68" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F68" t="n">
+        <v>-8651.5</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1308601</v>
+      </c>
+      <c r="H68" t="n">
+        <v>37962</v>
+      </c>
+    </row>
+    <row r="69" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-01-30 14:42:09</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>NIFTY2620325550CE</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>122.35</v>
+      </c>
+      <c r="D69" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F69" t="n">
+        <v>-8651.5</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1000836</v>
+      </c>
+      <c r="H69" t="n">
+        <v>37724</v>
+      </c>
+    </row>
+    <row r="70" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-01-30 15:13:35</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>NIFTY2620325550CE</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="D70" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F70" t="n">
+        <v>572</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1137642</v>
+      </c>
+      <c r="H70" t="n">
+        <v>35032</v>
+      </c>
+    </row>
+    <row r="71" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-01-30 15:15:39</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>NIFTY2620325250PE</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>153.1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>146.05</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-10081.5</v>
+      </c>
+      <c r="G71" t="n">
+        <v>3086750</v>
+      </c>
+      <c r="H71" t="n">
+        <v>53826</v>
+      </c>
+    </row>
+    <row r="72" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-01-30 15:18:49</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>NIFTY2620325600CE</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="D72" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1072.5</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1834211</v>
+      </c>
+      <c r="H72" t="n">
+        <v>77903</v>
+      </c>
+    </row>
+    <row r="73" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-01-30 15:20:49</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>NIFTY2620325200PE</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>128.65</v>
+      </c>
+      <c r="D73" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1215.5</v>
+      </c>
+      <c r="G73" t="n">
+        <v>3584896</v>
+      </c>
+      <c r="H73" t="n">
+        <v>83853</v>
+      </c>
+    </row>
+    <row r="74" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-01-30 15:24:28</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>NIFTY2620325150PE</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>115.15</v>
+      </c>
+      <c r="D74" t="n">
+        <v>115.85</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1001</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1499545</v>
+      </c>
+      <c r="H74" t="n">
+        <v>29840</v>
+      </c>
+    </row>
+    <row r="75" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-01-30 15:26:45</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>NIFTY2620325150PE</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>115.45</v>
+      </c>
+      <c r="D75" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-8580</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1507550</v>
+      </c>
+      <c r="H75" t="n">
+        <v>28413</v>
+      </c>
+    </row>
+    <row r="76" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-02-02 11:16:07</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>NIFTY2620324750PE</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>141.15</v>
+      </c>
+      <c r="D76" t="n">
+        <v>141.95</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1144</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1735202</v>
+      </c>
+      <c r="H76" t="n">
+        <v>88134</v>
+      </c>
+    </row>
+    <row r="77" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-02-02 11:19:45</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>NIFTY2620324700PE</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>126.7</v>
+      </c>
+      <c r="D77" t="n">
+        <v>127.4</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1001</v>
+      </c>
+      <c r="G77" t="n">
+        <v>2684929</v>
+      </c>
+      <c r="H77" t="n">
+        <v>174484</v>
+      </c>
+    </row>
+    <row r="78" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-02-02 11:22:38</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>NIFTY2620324700PE</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="D78" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2753783</v>
+      </c>
+      <c r="H78" t="n">
+        <v>176013</v>
+      </c>
+    </row>
+    <row r="79" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-02-02 11:24:44</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>NIFTY2620324650PE</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>112.75</v>
+      </c>
+      <c r="D79" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1072.5</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1282362</v>
+      </c>
+      <c r="H79" t="n">
+        <v>65627</v>
+      </c>
+    </row>
+    <row r="80" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-02-02 11:26:21</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>NIFTY2620324700CE</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>132.55</v>
+      </c>
+      <c r="D80" t="n">
+        <v>133.8</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1787.5</v>
+      </c>
+      <c r="G80" t="n">
+        <v>710436</v>
+      </c>
+      <c r="H80" t="n">
+        <v>75014</v>
+      </c>
+    </row>
+    <row r="81" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-02-02 11:28:42</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>NIFTY2620324700CE</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>132.7</v>
+      </c>
+      <c r="D81" t="n">
+        <v>133.45</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1072.5</v>
+      </c>
+      <c r="G81" t="n">
+        <v>749524</v>
+      </c>
+      <c r="H81" t="n">
+        <v>75014</v>
+      </c>
+    </row>
+    <row r="82" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-02-02 11:30:29</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>NIFTY2620324750CE</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>119.6</v>
+      </c>
+      <c r="D82" t="n">
+        <v>120.7</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1573</v>
+      </c>
+      <c r="G82" t="n">
+        <v>827020</v>
+      </c>
+      <c r="H82" t="n">
+        <v>79353</v>
+      </c>
+    </row>
+    <row r="83" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-02-02 11:32:04</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>NIFTY2620324750CE</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>123.35</v>
+      </c>
+      <c r="D83" t="n">
+        <v>124.25</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1287</v>
+      </c>
+      <c r="G83" t="n">
+        <v>884248</v>
+      </c>
+      <c r="H83" t="n">
+        <v>79974</v>
+      </c>
+    </row>
+    <row r="84" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-02-02 11:34:57</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>NIFTY2620324850CE</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="D84" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1859</v>
+      </c>
+      <c r="G84" t="n">
+        <v>2156538</v>
+      </c>
+      <c r="H84" t="n">
+        <v>104912</v>
+      </c>
+    </row>
+    <row r="85" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-02-02 11:37:27</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>NIFTY2620324800PE</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="D85" t="n">
+        <v>115.6</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F85" t="n">
+        <v>-9009</v>
+      </c>
+      <c r="G85" t="n">
+        <v>4018207</v>
+      </c>
+      <c r="H85" t="n">
+        <v>138636</v>
+      </c>
+    </row>
+    <row r="86" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-02-05 12:55:47</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>NIFTY2621025600PE</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>117.35</v>
+      </c>
+      <c r="D86" t="n">
+        <v>118.25</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1287</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1806853</v>
+      </c>
+      <c r="H86" t="n">
+        <v>103248</v>
+      </c>
+    </row>
+    <row r="87" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-02-05 12:59:49</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>NIFTY2621025700CE</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>117</v>
+      </c>
+      <c r="D87" t="n">
+        <v>120.75</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F87" t="n">
+        <v>5362.5</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1933396</v>
+      </c>
+      <c r="H87" t="n">
+        <v>191129</v>
+      </c>
+    </row>
+    <row r="88" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-02-05 13:01:32</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>NIFTY2621025650PE</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>132.1</v>
+      </c>
+      <c r="D88" t="n">
+        <v>133.4</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1859</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1658438</v>
+      </c>
+      <c r="H88" t="n">
+        <v>64251</v>
+      </c>
+    </row>
+    <row r="89" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-02-05 13:04:29</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>NIFTY2621025650PE</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>131.3</v>
+      </c>
+      <c r="D89" t="n">
+        <v>131.85</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F89" t="n">
+        <v>786.5</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1664505</v>
+      </c>
+      <c r="H89" t="n">
+        <v>65572</v>
+      </c>
+    </row>
+    <row r="90" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-02-05 13:06:21</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>NIFTY2621025700CE</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>120.65</v>
+      </c>
+      <c r="D90" t="n">
+        <v>121.55</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1287</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1977093</v>
+      </c>
+      <c r="H90" t="n">
+        <v>189314</v>
+      </c>
+    </row>
+    <row r="91" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-02-05 13:09:50</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>NIFTY2621025700CE</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="D91" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1859</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1987523</v>
+      </c>
+      <c r="H91" t="n">
+        <v>189314</v>
+      </c>
+    </row>
+    <row r="92" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-02-05 13:17:43</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>NIFTY2621025700CE</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>119.4</v>
+      </c>
+      <c r="D92" t="n">
+        <v>120.35</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1358.5</v>
+      </c>
+      <c r="G92" t="n">
+        <v>2007315</v>
+      </c>
+      <c r="H92" t="n">
+        <v>191845</v>
+      </c>
+    </row>
+    <row r="93" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-02-05 13:20:19</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>NIFTY2621025700CE</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="D93" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F93" t="n">
+        <v>715</v>
+      </c>
+      <c r="G93" t="n">
+        <v>2046281</v>
+      </c>
+      <c r="H93" t="n">
+        <v>190747</v>
+      </c>
+    </row>
+    <row r="94" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-02-05 13:22:15</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>NIFTY2621025700CE</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="D94" t="n">
+        <v>121.2</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F94" t="n">
+        <v>572</v>
+      </c>
+      <c r="G94" t="n">
+        <v>2055866</v>
+      </c>
+      <c r="H94" t="n">
+        <v>191410</v>
+      </c>
+    </row>
+    <row r="95" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-02-05 13:25:17</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>NIFTY2621025700CE</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="D95" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F95" t="n">
+        <v>-8580</v>
+      </c>
+      <c r="G95" t="n">
+        <v>2065658</v>
+      </c>
+      <c r="H95" t="n">
+        <v>190871</v>
+      </c>
+    </row>
+    <row r="96" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-02-05 13:26:56</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>NIFTY2621025600PE</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="D96" t="n">
+        <v>113.55</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F96" t="n">
+        <v>429</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1997094</v>
+      </c>
+      <c r="H96" t="n">
+        <v>105347</v>
+      </c>
+    </row>
+    <row r="97" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-02-05 13:28:55</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>NIFTY2621025650PE</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>141.9</v>
+      </c>
+      <c r="D97" t="n">
+        <v>143.6</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F97" t="n">
+        <v>2431</v>
+      </c>
+      <c r="G97" t="n">
+        <v>1774758</v>
+      </c>
+      <c r="H97" t="n">
+        <v>68200</v>
+      </c>
+    </row>
+    <row r="98" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-02-05 13:32:45</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>NIFTY2621025600PE</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>123.3</v>
+      </c>
+      <c r="D98" t="n">
+        <v>116.75</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F98" t="n">
+        <v>-9366.5</v>
+      </c>
+      <c r="G98" t="n">
+        <v>2051826</v>
+      </c>
+      <c r="H98" t="n">
+        <v>101564</v>
+      </c>
+    </row>
+    <row r="99" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-02-05 13:35:52</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>NIFTY2621025700CE</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>115.25</v>
+      </c>
+      <c r="D99" t="n">
+        <v>115.75</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F99" t="n">
+        <v>715</v>
+      </c>
+      <c r="G99" t="n">
+        <v>2145900</v>
+      </c>
+      <c r="H99" t="n">
+        <v>193807</v>
+      </c>
+    </row>
+    <row r="100" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-02-05 13:38:06</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>NIFTY2621025700CE</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>114.85</v>
+      </c>
+      <c r="D100" t="n">
+        <v>115.85</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1430</v>
+      </c>
+      <c r="G100" t="n">
+        <v>2155850</v>
+      </c>
+      <c r="H100" t="n">
+        <v>193807</v>
+      </c>
+    </row>
+    <row r="101" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-02-05 13:48:10</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>NIFTY2621025700CE</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>118.7</v>
+      </c>
+      <c r="D101" t="n">
+        <v>119.8</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1573</v>
+      </c>
+      <c r="G101" t="n">
+        <v>2177187</v>
+      </c>
+      <c r="H101" t="n">
+        <v>189851</v>
+      </c>
+    </row>
     <row r="102" ht="19.95" customFormat="1" customHeight="1" s="1"/>
     <row r="103" ht="19.95" customFormat="1" customHeight="1" s="1"/>
     <row r="104" ht="19.95" customFormat="1" customHeight="1" s="1"/>

--- a/Lakshmi1.xlsx
+++ b/Lakshmi1.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.6"/>
   <cols>
     <col width="21.109375" customWidth="1" style="1" min="1" max="2"/>
@@ -3486,58 +3486,1566 @@
         <v>189851</v>
       </c>
     </row>
-    <row r="102" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="103" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="104" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="105" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="106" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="107" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="108" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="109" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="110" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="111" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="112" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="113" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="114" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="115" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="116" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="117" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="118" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="119" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="120" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="121" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="122" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="123" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="124" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="125" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="126" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="127" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="128" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="129" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="130" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="131" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="132" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="133" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="134" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="135" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="136" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="137" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="138" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="139" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="140" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="141" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="142" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="143" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="144" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="145" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="146" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="147" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="148" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="149" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="150" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="151" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="152" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="153" ht="19.95" customFormat="1" customHeight="1" s="1"/>
+    <row r="102" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-02-11 12:54:27</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>NIFTY2621726000PE</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>151.25</v>
+      </c>
+      <c r="D102" t="n">
+        <v>145</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F102" t="n">
+        <v>-8937.5</v>
+      </c>
+      <c r="G102" t="n">
+        <v>2584364</v>
+      </c>
+      <c r="H102" t="n">
+        <v>113800</v>
+      </c>
+    </row>
+    <row r="103" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-02-11 12:57:17</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>NIFTY2621725950CE</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>119.75</v>
+      </c>
+      <c r="D103" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1215.5</v>
+      </c>
+      <c r="G103" t="n">
+        <v>1566595</v>
+      </c>
+      <c r="H103" t="n">
+        <v>141493</v>
+      </c>
+    </row>
+    <row r="104" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-02-11 13:00:50</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>NIFTY2621725950PE</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="D104" t="n">
+        <v>120.05</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1787.5</v>
+      </c>
+      <c r="G104" t="n">
+        <v>2299915</v>
+      </c>
+      <c r="H104" t="n">
+        <v>93665</v>
+      </c>
+    </row>
+    <row r="105" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-02-11 13:03:28</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>NIFTY2621725950PE</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="D105" t="n">
+        <v>125</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1287</v>
+      </c>
+      <c r="G105" t="n">
+        <v>2335379</v>
+      </c>
+      <c r="H105" t="n">
+        <v>96084</v>
+      </c>
+    </row>
+    <row r="106" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-02-11 13:06:49</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>NIFTY2621725950CE</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>117.95</v>
+      </c>
+      <c r="D106" t="n">
+        <v>119.7</v>
+      </c>
+      <c r="E106" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F106" t="n">
+        <v>2502.5</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1625867</v>
+      </c>
+      <c r="H106" t="n">
+        <v>138671</v>
+      </c>
+    </row>
+    <row r="107" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-02-11 13:20:43</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>NIFTY2621725950CE</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="D107" t="n">
+        <v>124</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F107" t="n">
+        <v>3003</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1639238</v>
+      </c>
+      <c r="H107" t="n">
+        <v>138565</v>
+      </c>
+    </row>
+    <row r="108" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-02-11 13:23:57</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>NIFTY2621725950PE</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>116.1</v>
+      </c>
+      <c r="D108" t="n">
+        <v>117.15</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1501.5</v>
+      </c>
+      <c r="G108" t="n">
+        <v>2440817</v>
+      </c>
+      <c r="H108" t="n">
+        <v>98544</v>
+      </c>
+    </row>
+    <row r="109" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-02-11 13:27:25</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>NIFTY2621725950CE</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="D109" t="n">
+        <v>124.6</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F109" t="n">
+        <v>715</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1722761</v>
+      </c>
+      <c r="H109" t="n">
+        <v>138622</v>
+      </c>
+    </row>
+    <row r="110" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-02-11 13:30:20</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>NIFTY2621725950CE</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>129.05</v>
+      </c>
+      <c r="D110" t="n">
+        <v>130.1</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1501.5</v>
+      </c>
+      <c r="G110" t="n">
+        <v>1757525</v>
+      </c>
+      <c r="H110" t="n">
+        <v>135537</v>
+      </c>
+    </row>
+    <row r="111" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-02-11 13:35:47</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>NIFTY2621726000PE</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>132.15</v>
+      </c>
+      <c r="D111" t="n">
+        <v>126</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F111" t="n">
+        <v>-8794.5</v>
+      </c>
+      <c r="G111" t="n">
+        <v>2823163</v>
+      </c>
+      <c r="H111" t="n">
+        <v>123045</v>
+      </c>
+    </row>
+    <row r="112" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-02-11 13:41:11</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>NIFTY2621725950CE</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>133.9</v>
+      </c>
+      <c r="D112" t="n">
+        <v>135.05</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1644.5</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1838741</v>
+      </c>
+      <c r="H112" t="n">
+        <v>127342</v>
+      </c>
+    </row>
+    <row r="113" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-02-11 13:44:49</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>NIFTY2621726000CE</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>113.05</v>
+      </c>
+      <c r="D113" t="n">
+        <v>107</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F113" t="n">
+        <v>-8651.5</v>
+      </c>
+      <c r="G113" t="n">
+        <v>3212285</v>
+      </c>
+      <c r="H113" t="n">
+        <v>275775</v>
+      </c>
+    </row>
+    <row r="114" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-02-11 13:47:16</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>NIFTY2621726000PE</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>124.65</v>
+      </c>
+      <c r="D114" t="n">
+        <v>125.15</v>
+      </c>
+      <c r="E114" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F114" t="n">
+        <v>715</v>
+      </c>
+      <c r="G114" t="n">
+        <v>2952991</v>
+      </c>
+      <c r="H114" t="n">
+        <v>131439</v>
+      </c>
+    </row>
+    <row r="115" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-02-11 13:49:26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>NIFTY2621726000PE</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>127.75</v>
+      </c>
+      <c r="D115" t="n">
+        <v>129.1</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1930.5</v>
+      </c>
+      <c r="G115" t="n">
+        <v>2969039</v>
+      </c>
+      <c r="H115" t="n">
+        <v>135636</v>
+      </c>
+    </row>
+    <row r="116" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-02-11 13:51:52</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>NIFTY2621726000PE</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="D116" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F116" t="n">
+        <v>858</v>
+      </c>
+      <c r="G116" t="n">
+        <v>3004198</v>
+      </c>
+      <c r="H116" t="n">
+        <v>131887</v>
+      </c>
+    </row>
+    <row r="117" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-02-11 13:53:28</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>NIFTY2621725950PE</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="D117" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1001</v>
+      </c>
+      <c r="G117" t="n">
+        <v>2717807</v>
+      </c>
+      <c r="H117" t="n">
+        <v>105113</v>
+      </c>
+    </row>
+    <row r="118" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-02-11 13:57:03</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>NIFTY2621726000CE</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>94.84999999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1215.5</v>
+      </c>
+      <c r="G118" t="n">
+        <v>3379943</v>
+      </c>
+      <c r="H118" t="n">
+        <v>269620</v>
+      </c>
+    </row>
+    <row r="119" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-02-11 13:58:57</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>NIFTY2621725950PE</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="D119" t="n">
+        <v>112.35</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1501.5</v>
+      </c>
+      <c r="G119" t="n">
+        <v>2749959</v>
+      </c>
+      <c r="H119" t="n">
+        <v>103827</v>
+      </c>
+    </row>
+    <row r="120" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-02-11 14:06:33</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>NIFTY2621725950CE</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>123.4</v>
+      </c>
+      <c r="D120" t="n">
+        <v>123.8</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F120" t="n">
+        <v>572</v>
+      </c>
+      <c r="G120" t="n">
+        <v>2002572</v>
+      </c>
+      <c r="H120" t="n">
+        <v>121187</v>
+      </c>
+    </row>
+    <row r="121" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-02-11 14:10:51</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>NIFTY2621725950PE</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>110</v>
+      </c>
+      <c r="D121" t="n">
+        <v>104</v>
+      </c>
+      <c r="E121" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F121" t="n">
+        <v>-8580</v>
+      </c>
+      <c r="G121" t="n">
+        <v>2815853</v>
+      </c>
+      <c r="H121" t="n">
+        <v>102393</v>
+      </c>
+    </row>
+    <row r="122" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-02-11 14:14:08</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>NIFTY2621725950CE</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>127.75</v>
+      </c>
+      <c r="D122" t="n">
+        <v>130.2</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F122" t="n">
+        <v>3503.5</v>
+      </c>
+      <c r="G122" t="n">
+        <v>2056317</v>
+      </c>
+      <c r="H122" t="n">
+        <v>123093</v>
+      </c>
+    </row>
+    <row r="123" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-02-11 14:16:03</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>NIFTY2621725950CE</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>135.55</v>
+      </c>
+      <c r="D123" t="n">
+        <v>135.9</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F123" t="n">
+        <v>500.5</v>
+      </c>
+      <c r="G123" t="n">
+        <v>2084382</v>
+      </c>
+      <c r="H123" t="n">
+        <v>121665</v>
+      </c>
+    </row>
+    <row r="124" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-02-11 14:18:13</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>NIFTY2621725950CE</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>136.1</v>
+      </c>
+      <c r="D124" t="n">
+        <v>137.25</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1644.5</v>
+      </c>
+      <c r="G124" t="n">
+        <v>2101379</v>
+      </c>
+      <c r="H124" t="n">
+        <v>121665</v>
+      </c>
+    </row>
+    <row r="125" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-02-11 14:20:37</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>NIFTY2621726000PE</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="D125" t="n">
+        <v>124.8</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1287</v>
+      </c>
+      <c r="G125" t="n">
+        <v>3181574</v>
+      </c>
+      <c r="H125" t="n">
+        <v>127945</v>
+      </c>
+    </row>
+    <row r="126" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-02-11 14:23:11</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>NIFTY2621726000PE</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>128.7</v>
+      </c>
+      <c r="D126" t="n">
+        <v>132.6</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F126" t="n">
+        <v>5577</v>
+      </c>
+      <c r="G126" t="n">
+        <v>3211744</v>
+      </c>
+      <c r="H126" t="n">
+        <v>131527</v>
+      </c>
+    </row>
+    <row r="127" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-02-11 14:28:46</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>NIFTY2621726000PE</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>132.55</v>
+      </c>
+      <c r="D127" t="n">
+        <v>126.35</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-8866</v>
+      </c>
+      <c r="G127" t="n">
+        <v>3236260</v>
+      </c>
+      <c r="H127" t="n">
+        <v>130609</v>
+      </c>
+    </row>
+    <row r="128" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-02-11 14:32:13</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>NIFTY2621726000PE</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>134.95</v>
+      </c>
+      <c r="D128" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F128" t="n">
+        <v>-9223.5</v>
+      </c>
+      <c r="G128" t="n">
+        <v>3271465</v>
+      </c>
+      <c r="H128" t="n">
+        <v>128622</v>
+      </c>
+    </row>
+    <row r="129" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-02-11 14:36:21</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>NIFTY2621725950CE</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>130.4</v>
+      </c>
+      <c r="D129" t="n">
+        <v>131.1</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1001</v>
+      </c>
+      <c r="G129" t="n">
+        <v>2207996</v>
+      </c>
+      <c r="H129" t="n">
+        <v>114950</v>
+      </c>
+    </row>
+    <row r="130" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-02-11 14:42:06</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>NIFTY2621725950CE</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="D130" t="n">
+        <v>124.45</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F130" t="n">
+        <v>-8651.5</v>
+      </c>
+      <c r="G130" t="n">
+        <v>2225223</v>
+      </c>
+      <c r="H130" t="n">
+        <v>115650</v>
+      </c>
+    </row>
+    <row r="131" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-02-13 11:36:56</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>NIFTY2621725600PE</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>123</v>
+      </c>
+      <c r="D131" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="E131" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F131" t="n">
+        <v>2145</v>
+      </c>
+      <c r="G131" t="n">
+        <v>3369690</v>
+      </c>
+      <c r="H131" t="n">
+        <v>148015</v>
+      </c>
+    </row>
+    <row r="132" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-02-13 11:41:29</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>NIFTY2621725500CE</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>136.9</v>
+      </c>
+      <c r="D132" t="n">
+        <v>130.35</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F132" t="n">
+        <v>-9366.5</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1219743</v>
+      </c>
+      <c r="H132" t="n">
+        <v>152223</v>
+      </c>
+    </row>
+    <row r="133" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-02-13 11:44:21</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>NIFTY2621725500CE</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>138.05</v>
+      </c>
+      <c r="D133" t="n">
+        <v>139.05</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1430</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1260208</v>
+      </c>
+      <c r="H133" t="n">
+        <v>154258</v>
+      </c>
+    </row>
+    <row r="134" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-02-13 11:49:13</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>NIFTY2621725600PE</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>116.55</v>
+      </c>
+      <c r="D134" t="n">
+        <v>117.65</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1573</v>
+      </c>
+      <c r="G134" t="n">
+        <v>3474760</v>
+      </c>
+      <c r="H134" t="n">
+        <v>142549</v>
+      </c>
+    </row>
+    <row r="135" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:02:39</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>NIFTY2621725600PE</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>113.6</v>
+      </c>
+      <c r="D135" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F135" t="n">
+        <v>-8651.5</v>
+      </c>
+      <c r="G135" t="n">
+        <v>3580320</v>
+      </c>
+      <c r="H135" t="n">
+        <v>150053</v>
+      </c>
+    </row>
+    <row r="136" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:05:15</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>NIFTY2621725550CE</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="D136" t="n">
+        <v>116</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F136" t="n">
+        <v>858</v>
+      </c>
+      <c r="G136" t="n">
+        <v>1537672</v>
+      </c>
+      <c r="H136" t="n">
+        <v>143187</v>
+      </c>
+    </row>
+    <row r="137" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:06:57</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>NIFTY2621725550CE</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="D137" t="n">
+        <v>119.95</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F137" t="n">
+        <v>2073.5</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1551648</v>
+      </c>
+      <c r="H137" t="n">
+        <v>138370</v>
+      </c>
+    </row>
+    <row r="138" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:10:10</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>NIFTY2621725600PE</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="D138" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F138" t="n">
+        <v>2502.5</v>
+      </c>
+      <c r="G138" t="n">
+        <v>3703728</v>
+      </c>
+      <c r="H138" t="n">
+        <v>163712</v>
+      </c>
+    </row>
+    <row r="139" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:13:04</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>NIFTY2621725550CE</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>118.45</v>
+      </c>
+      <c r="D139" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F139" t="n">
+        <v>929.5</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1609772</v>
+      </c>
+      <c r="H139" t="n">
+        <v>131641</v>
+      </c>
+    </row>
+    <row r="140" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:15:50</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>NIFTY2621725650PE</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>134.7</v>
+      </c>
+      <c r="D140" t="n">
+        <v>135.6</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1287</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1208675</v>
+      </c>
+      <c r="H140" t="n">
+        <v>79507</v>
+      </c>
+    </row>
+    <row r="141" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:17:30</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>NIFTY2621725600PE</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>108.85</v>
+      </c>
+      <c r="D141" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="E141" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F141" t="n">
+        <v>429</v>
+      </c>
+      <c r="G141" t="n">
+        <v>3778965</v>
+      </c>
+      <c r="H141" t="n">
+        <v>171883</v>
+      </c>
+    </row>
+    <row r="142" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:19:48</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>NIFTY2621725500CE</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>150.25</v>
+      </c>
+      <c r="D142" t="n">
+        <v>151</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1072.5</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1494649</v>
+      </c>
+      <c r="H142" t="n">
+        <v>134703</v>
+      </c>
+    </row>
+    <row r="143" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:24:17</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>NIFTY2621725550CE</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>122.8</v>
+      </c>
+      <c r="D143" t="n">
+        <v>123.25</v>
+      </c>
+      <c r="E143" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F143" t="n">
+        <v>643.5</v>
+      </c>
+      <c r="G143" t="n">
+        <v>1669762</v>
+      </c>
+      <c r="H143" t="n">
+        <v>126419</v>
+      </c>
+    </row>
+    <row r="144" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:26:09</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>NIFTY2621725550CE</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>123.85</v>
+      </c>
+      <c r="D144" t="n">
+        <v>124.35</v>
+      </c>
+      <c r="E144" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F144" t="n">
+        <v>715</v>
+      </c>
+      <c r="G144" t="n">
+        <v>1696935</v>
+      </c>
+      <c r="H144" t="n">
+        <v>125555</v>
+      </c>
+    </row>
+    <row r="145" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:27:55</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>NIFTY2621725600CE</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="D145" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="E145" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1358.5</v>
+      </c>
+      <c r="G145" t="n">
+        <v>3266383</v>
+      </c>
+      <c r="H145" t="n">
+        <v>314681</v>
+      </c>
+    </row>
+    <row r="146" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:34:06</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>NIFTY2621725550CE</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>131.45</v>
+      </c>
+      <c r="D146" t="n">
+        <v>132.2</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1072.5</v>
+      </c>
+      <c r="G146" t="n">
+        <v>1776283</v>
+      </c>
+      <c r="H146" t="n">
+        <v>106843</v>
+      </c>
+    </row>
+    <row r="147" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:37:16</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>NIFTY2621725650PE</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>125.2</v>
+      </c>
+      <c r="D147" t="n">
+        <v>126.1</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1287</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1354614</v>
+      </c>
+      <c r="H147" t="n">
+        <v>89076</v>
+      </c>
+    </row>
+    <row r="148" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:39:39</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>NIFTY2621725650PE</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>124.7</v>
+      </c>
+      <c r="D148" t="n">
+        <v>125.2</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F148" t="n">
+        <v>715</v>
+      </c>
+      <c r="G148" t="n">
+        <v>1367035</v>
+      </c>
+      <c r="H148" t="n">
+        <v>90572</v>
+      </c>
+    </row>
+    <row r="149" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:42:03</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>NIFTY2621725650PE</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>128</v>
+      </c>
+      <c r="D149" t="n">
+        <v>128.55</v>
+      </c>
+      <c r="E149" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F149" t="n">
+        <v>786.5</v>
+      </c>
+      <c r="G149" t="n">
+        <v>1375439</v>
+      </c>
+      <c r="H149" t="n">
+        <v>89681</v>
+      </c>
+    </row>
+    <row r="150" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:46:09</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>NIFTY2621725650PE</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>127.75</v>
+      </c>
+      <c r="D150" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="E150" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F150" t="n">
+        <v>-8794.5</v>
+      </c>
+      <c r="G150" t="n">
+        <v>1386630</v>
+      </c>
+      <c r="H150" t="n">
+        <v>89681</v>
+      </c>
+    </row>
+    <row r="151" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:48:14</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>NIFTY2621725550CE</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>133.25</v>
+      </c>
+      <c r="D151" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F151" t="n">
+        <v>-8794.5</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1931083</v>
+      </c>
+      <c r="H151" t="n">
+        <v>94112</v>
+      </c>
+    </row>
+    <row r="152" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:50:34</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>NIFTY2621725650PE</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>132.45</v>
+      </c>
+      <c r="D152" t="n">
+        <v>133.75</v>
+      </c>
+      <c r="E152" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1859</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1427213</v>
+      </c>
+      <c r="H152" t="n">
+        <v>89744</v>
+      </c>
+    </row>
+    <row r="153" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:52:11</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>NIFTY2621725650PE</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>132.9</v>
+      </c>
+      <c r="D153" t="n">
+        <v>133.15</v>
+      </c>
+      <c r="E153" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F153" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="G153" t="n">
+        <v>1447914</v>
+      </c>
+      <c r="H153" t="n">
+        <v>83036</v>
+      </c>
+    </row>
     <row r="154" ht="19.95" customFormat="1" customHeight="1" s="1"/>
     <row r="155" ht="19.95" customFormat="1" customHeight="1" s="1"/>
     <row r="156" ht="19.95" customFormat="1" customHeight="1" s="1"/>

--- a/Lakshmi1.xlsx
+++ b/Lakshmi1.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H153"/>
+  <dimension ref="A1:H155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.6"/>
   <cols>
     <col width="21.109375" customWidth="1" style="1" min="1" max="2"/>
@@ -5046,8 +5046,66 @@
         <v>83036</v>
       </c>
     </row>
-    <row r="154" ht="19.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="155" ht="19.95" customFormat="1" customHeight="1" s="1"/>
+    <row r="154" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:08:08</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>NIFTY2631723000PE</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>110.05</v>
+      </c>
+      <c r="D154" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="E154" t="n">
+        <v>715</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1751.75</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1223596</v>
+      </c>
+      <c r="H154" t="n">
+        <v>113618</v>
+      </c>
+    </row>
+    <row r="155" ht="19.95" customFormat="1" customHeight="1" s="1">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:21:33</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>NIFTY2631723600CE</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>131.3</v>
+      </c>
+      <c r="D155" t="n">
+        <v>131.6</v>
+      </c>
+      <c r="E155" t="n">
+        <v>715</v>
+      </c>
+      <c r="F155" t="n">
+        <v>214.5</v>
+      </c>
+      <c r="G155" t="n">
+        <v>635081</v>
+      </c>
+      <c r="H155" t="n">
+        <v>100344</v>
+      </c>
+    </row>
     <row r="156" ht="19.95" customFormat="1" customHeight="1" s="1"/>
     <row r="157" ht="19.95" customFormat="1" customHeight="1" s="1"/>
     <row r="158" ht="19.95" customFormat="1" customHeight="1" s="1"/>
